--- a/src/results/Terstruktur(Data Scrapping).xlsx
+++ b/src/results/Terstruktur(Data Scrapping).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\PEI\Dashboard-Pertamina-VeloCT\src\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339183D5-8F5F-4D1D-B5A6-15D104FEC948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3AC8DD-7261-4272-B5F1-B380C359E48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/results/Terstruktur(Data Scrapping).xlsx
+++ b/src/results/Terstruktur(Data Scrapping).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\PEI\Dashboard-Pertamina-VeloCT\src\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pekerjaan\Dashboard-Pertamina-VeloCT\src\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3AC8DD-7261-4272-B5F1-B380C359E48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76E9B2D-5D7A-4D6C-8651-FCB0631E8F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="290" yWindow="1900" windowWidth="18910" windowHeight="9820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(Data)Biodesel" sheetId="1" r:id="rId1"/>
@@ -18,25 +18,12 @@
     <sheet name="(Data)eia" sheetId="3" r:id="rId3"/>
     <sheet name="(Data)CPO" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="369">
   <si>
     <t>Date</t>
   </si>
@@ -911,21 +898,204 @@
     <t>Tanggal</t>
   </si>
   <si>
+    <t>Januari</t>
+  </si>
+  <si>
+    <t>1 Februari</t>
+  </si>
+  <si>
+    <t>Februari</t>
+  </si>
+  <si>
+    <t>1 Maret</t>
+  </si>
+  <si>
+    <t>Maret</t>
+  </si>
+  <si>
+    <t>1 April</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>6 Mei</t>
+  </si>
+  <si>
+    <t>Mei</t>
+  </si>
+  <si>
+    <t>1 Juni</t>
+  </si>
+  <si>
+    <t>Juni</t>
+  </si>
+  <si>
+    <t>3 Juli</t>
+  </si>
+  <si>
+    <t>Juli</t>
+  </si>
+  <si>
+    <t>1 Agustus</t>
+  </si>
+  <si>
     <t>Agustus</t>
   </si>
   <si>
+    <t>2 September</t>
+  </si>
+  <si>
     <t>September</t>
   </si>
   <si>
+    <t>7 Oktober</t>
+  </si>
+  <si>
+    <t>Oktober</t>
+  </si>
+  <si>
+    <t>4 November</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>4 Desember</t>
+  </si>
+  <si>
+    <t>Desember</t>
+  </si>
+  <si>
+    <t>2 Januari</t>
+  </si>
+  <si>
+    <t>5 Februari</t>
+  </si>
+  <si>
+    <t>5 Maret</t>
+  </si>
+  <si>
+    <t>8 Mei</t>
+  </si>
+  <si>
+    <t>5 Juni</t>
+  </si>
+  <si>
+    <t>2 Juli</t>
+  </si>
+  <si>
+    <t>5 Agustus</t>
+  </si>
+  <si>
+    <t>3 September</t>
+  </si>
+  <si>
+    <t>2 Oktober</t>
+  </si>
+  <si>
+    <t>6 November</t>
+  </si>
+  <si>
+    <t>6 Januari</t>
+  </si>
+  <si>
+    <t>2 Maret</t>
+  </si>
+  <si>
+    <t>5 April</t>
+  </si>
+  <si>
+    <t>4 Mei</t>
+  </si>
+  <si>
+    <t>4 Juni</t>
+  </si>
+  <si>
+    <t>3 Agustus</t>
+  </si>
+  <si>
+    <t>4 Oktober</t>
+  </si>
+  <si>
+    <t>8 November</t>
+  </si>
+  <si>
+    <t>1 Desember</t>
+  </si>
+  <si>
+    <t>3 Januari</t>
+  </si>
+  <si>
+    <t>2 Februari</t>
+  </si>
+  <si>
+    <t>9 Mei</t>
+  </si>
+  <si>
+    <t>2 Juni</t>
+  </si>
+  <si>
+    <t>1 Juli</t>
+  </si>
+  <si>
+    <t>1 September</t>
+  </si>
+  <si>
+    <t>3 Oktober</t>
+  </si>
+  <si>
+    <t>1 November</t>
+  </si>
+  <si>
+    <t>3 April</t>
+  </si>
+  <si>
+    <t>2 Mei</t>
+  </si>
+  <si>
+    <t>1 Oktober</t>
+  </si>
+  <si>
+    <t>2 Desember</t>
+  </si>
+  <si>
+    <t>3 Juni</t>
+  </si>
+  <si>
+    <t>10 Desember</t>
+  </si>
+  <si>
+    <t>9 Januari</t>
+  </si>
+  <si>
+    <t>12 Februari</t>
+  </si>
+  <si>
+    <t>11 Maret</t>
+  </si>
+  <si>
+    <t>16 April</t>
+  </si>
+  <si>
+    <t>19 Mei</t>
+  </si>
+  <si>
+    <t>10 Juni</t>
+  </si>
+  <si>
+    <t>8 Agustus</t>
+  </si>
+  <si>
+    <t>10 September</t>
+  </si>
+  <si>
     <t>66.81</t>
   </si>
   <si>
     <t>8 Oktober</t>
   </si>
   <si>
-    <t>Oktober</t>
-  </si>
-  <si>
     <t>63.62</t>
   </si>
   <si>
@@ -956,203 +1126,21 @@
     <t>Non-OECD</t>
   </si>
   <si>
-    <t>Maret</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>Mei</t>
-  </si>
-  <si>
-    <t>Juni</t>
-  </si>
-  <si>
-    <t>Juli</t>
-  </si>
-  <si>
-    <t>November</t>
-  </si>
-  <si>
-    <t>Desember</t>
-  </si>
-  <si>
-    <t>Januari</t>
-  </si>
-  <si>
-    <t>Februari</t>
-  </si>
-  <si>
     <t>Dates</t>
   </si>
   <si>
     <t>PX_LAST</t>
-  </si>
-  <si>
-    <t>12 Februari</t>
-  </si>
-  <si>
-    <t>11 Maret</t>
-  </si>
-  <si>
-    <t>16 April</t>
-  </si>
-  <si>
-    <t>19 Mei</t>
-  </si>
-  <si>
-    <t>4 Juni</t>
-  </si>
-  <si>
-    <t>3 Juli</t>
-  </si>
-  <si>
-    <t>8 Agustus</t>
-  </si>
-  <si>
-    <t>10 September</t>
-  </si>
-  <si>
-    <t>10 Juni</t>
-  </si>
-  <si>
-    <t>9 Januari</t>
-  </si>
-  <si>
-    <t>10 Desember</t>
-  </si>
-  <si>
-    <t>1 November</t>
-  </si>
-  <si>
-    <t>1 Oktober</t>
-  </si>
-  <si>
-    <t>2 September</t>
-  </si>
-  <si>
-    <t>1 Agustus</t>
-  </si>
-  <si>
-    <t>1 Juli</t>
-  </si>
-  <si>
-    <t>3 Juni</t>
-  </si>
-  <si>
-    <t>2 Mei</t>
-  </si>
-  <si>
-    <t>1 April</t>
-  </si>
-  <si>
-    <t>1 Maret</t>
-  </si>
-  <si>
-    <t>1 Februari</t>
-  </si>
-  <si>
-    <t>2 Februari</t>
-  </si>
-  <si>
-    <t>5 Februari</t>
-  </si>
-  <si>
-    <t>2 Januari</t>
-  </si>
-  <si>
-    <t>2 Desember</t>
-  </si>
-  <si>
-    <t>1 September</t>
-  </si>
-  <si>
-    <t>5 Juni</t>
-  </si>
-  <si>
-    <t>3 April</t>
-  </si>
-  <si>
-    <t>1 Desember</t>
-  </si>
-  <si>
-    <t>3 Oktober</t>
-  </si>
-  <si>
-    <t>2 Juni</t>
-  </si>
-  <si>
-    <t>9 Mei</t>
-  </si>
-  <si>
-    <t>3 Januari</t>
-  </si>
-  <si>
-    <t>8 November</t>
-  </si>
-  <si>
-    <t>4 Oktober</t>
-  </si>
-  <si>
-    <t>3 Agustus</t>
-  </si>
-  <si>
-    <t>2 Juli</t>
-  </si>
-  <si>
-    <t>4 Mei</t>
-  </si>
-  <si>
-    <t>5 April</t>
-  </si>
-  <si>
-    <t>2 Maret</t>
-  </si>
-  <si>
-    <t>6 Januari</t>
-  </si>
-  <si>
-    <t>4 Desember</t>
-  </si>
-  <si>
-    <t>6 November</t>
-  </si>
-  <si>
-    <t>2 Oktober</t>
-  </si>
-  <si>
-    <t>3 September</t>
-  </si>
-  <si>
-    <t>5 Agustus</t>
-  </si>
-  <si>
-    <t>8 Mei</t>
-  </si>
-  <si>
-    <t>5 Maret</t>
-  </si>
-  <si>
-    <t>4 November</t>
-  </si>
-  <si>
-    <t>7 Oktober</t>
-  </si>
-  <si>
-    <t>1 Juni</t>
-  </si>
-  <si>
-    <t>6 Mei</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1166,11 +1154,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -1197,7 +1180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1235,58 +1218,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1591,12 +1538,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C143"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1618,7 +1562,7 @@
         <v>10143</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1629,7 +1573,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1640,7 +1584,7 @@
         <v>8794</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1651,7 +1595,7 @@
         <v>8939</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1662,7 +1606,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1673,7 +1617,7 @@
         <v>9343</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1684,7 +1628,7 @@
         <v>9112</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1695,7 +1639,7 @@
         <v>8954</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1706,7 +1650,7 @@
         <v>8922</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1717,7 +1661,7 @@
         <v>8770</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1728,7 +1672,7 @@
         <v>7829</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1739,7 +1683,7 @@
         <v>7494</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1750,7 +1694,7 @@
         <v>6478</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1761,7 +1705,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1772,7 +1716,7 @@
         <v>9456</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1783,7 +1727,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1794,7 +1738,7 @@
         <v>9271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1805,7 +1749,7 @@
         <v>9081</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1816,7 +1760,7 @@
         <v>8189</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1827,7 +1771,7 @@
         <v>7680</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1838,7 +1782,7 @@
         <v>6686</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1849,7 +1793,7 @@
         <v>6890</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1860,7 +1804,7 @@
         <v>7039</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1871,7 +1815,7 @@
         <v>6626</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -1882,7 +1826,7 @@
         <v>6954</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -1893,7 +1837,7 @@
         <v>7112</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -1904,7 +1848,7 @@
         <v>7687</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1915,7 +1859,7 @@
         <v>8026</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1926,7 +1870,7 @@
         <v>8891</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1937,7 +1881,7 @@
         <v>8737</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -1948,7 +1892,7 @@
         <v>8402</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1959,7 +1903,7 @@
         <v>7835</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -1970,7 +1914,7 @@
         <v>8483</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -1981,7 +1925,7 @@
         <v>9028</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -1992,7 +1936,7 @@
         <v>8262</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -2003,7 +1947,7 @@
         <v>8779</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -2014,7 +1958,7 @@
         <v>9362</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -2025,7 +1969,7 @@
         <v>9493</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -2036,7 +1980,7 @@
         <v>9358</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -2047,7 +1991,7 @@
         <v>8815</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -2058,7 +2002,7 @@
         <v>8230</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -2069,7 +2013,7 @@
         <v>8302</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -2080,7 +2024,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -2091,7 +2035,7 @@
         <v>7871</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2102,7 +2046,7 @@
         <v>7965</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2113,7 +2057,7 @@
         <v>8518</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -2124,7 +2068,7 @@
         <v>8490</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -2135,7 +2079,7 @@
         <v>8491</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -2146,7 +2090,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -2157,7 +2101,7 @@
         <v>7962</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>103</v>
       </c>
@@ -2168,7 +2112,7 @@
         <v>8161</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -2179,7 +2123,7 @@
         <v>8356</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -2190,7 +2134,7 @@
         <v>8261</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -2201,7 +2145,7 @@
         <v>8140</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>111</v>
       </c>
@@ -2212,7 +2156,7 @@
         <v>7949</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -2223,7 +2167,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2234,7 +2178,7 @@
         <v>7294</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -2245,7 +2189,7 @@
         <v>7341</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>119</v>
       </c>
@@ -2256,7 +2200,7 @@
         <v>7227</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2267,7 +2211,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -2278,7 +2222,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>125</v>
       </c>
@@ -2289,7 +2233,7 @@
         <v>7015</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -2300,7 +2244,7 @@
         <v>7403</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2311,7 +2255,7 @@
         <v>7387</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -2322,7 +2266,7 @@
         <v>7348</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -2333,7 +2277,7 @@
         <v>6977</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>135</v>
       </c>
@@ -2344,7 +2288,7 @@
         <v>6970</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -2355,7 +2299,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -2366,7 +2310,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -2377,7 +2321,7 @@
         <v>7358</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -2388,7 +2332,7 @@
         <v>7157</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -2399,7 +2343,7 @@
         <v>7914</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>147</v>
       </c>
@@ -2410,7 +2354,7 @@
         <v>8706</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -2421,7 +2365,7 @@
         <v>9539</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -2432,7 +2376,7 @@
         <v>8933</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2443,7 +2387,7 @@
         <v>8019</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -2454,7 +2398,7 @@
         <v>8352</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -2465,7 +2409,7 @@
         <v>6941</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -2476,7 +2420,7 @@
         <v>7321</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>161</v>
       </c>
@@ -2487,7 +2431,7 @@
         <v>7887</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2498,7 +2442,7 @@
         <v>9003</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -2509,7 +2453,7 @@
         <v>9265</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -2520,7 +2464,7 @@
         <v>9329</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>169</v>
       </c>
@@ -2531,7 +2475,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>171</v>
       </c>
@@ -2542,7 +2486,7 @@
         <v>9457</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>173</v>
       </c>
@@ -2553,7 +2497,7 @@
         <v>9579</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -2564,7 +2508,7 @@
         <v>9434</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>177</v>
       </c>
@@ -2575,7 +2519,7 @@
         <v>10131</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>179</v>
       </c>
@@ -2586,7 +2530,7 @@
         <v>10229</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -2597,7 +2541,7 @@
         <v>11034</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -2608,7 +2552,7 @@
         <v>9852</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>185</v>
       </c>
@@ -2619,7 +2563,7 @@
         <v>10635</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -2630,7 +2574,7 @@
         <v>11930</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>189</v>
       </c>
@@ -2641,7 +2585,7 @@
         <v>12022</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>191</v>
       </c>
@@ -2652,7 +2596,7 @@
         <v>12854</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>193</v>
       </c>
@@ -2663,7 +2607,7 @@
         <v>13746</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>195</v>
       </c>
@@ -2674,7 +2618,7 @@
         <v>13177</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -2685,7 +2629,7 @@
         <v>13867</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>199</v>
       </c>
@@ -2696,7 +2640,7 @@
         <v>14436</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>201</v>
       </c>
@@ -2707,7 +2651,7 @@
         <v>15559</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>203</v>
       </c>
@@ -2718,7 +2662,7 @@
         <v>15211</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>205</v>
       </c>
@@ -2729,7 +2673,7 @@
         <v>13033</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>207</v>
       </c>
@@ -2740,7 +2684,7 @@
         <v>11070</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>209</v>
       </c>
@@ -2751,7 +2695,7 @@
         <v>8047</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>211</v>
       </c>
@@ -2762,7 +2706,7 @@
         <v>10281</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>213</v>
       </c>
@@ -2773,7 +2717,7 @@
         <v>10787</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -2784,7 +2728,7 @@
         <v>11012</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>217</v>
       </c>
@@ -2795,7 +2739,7 @@
         <v>12039</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>219</v>
       </c>
@@ -2806,7 +2750,7 @@
         <v>11520</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>221</v>
       </c>
@@ -2817,7 +2761,7 @@
         <v>11233</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>223</v>
       </c>
@@ -2828,7 +2772,7 @@
         <v>11473</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>225</v>
       </c>
@@ -2839,7 +2783,7 @@
         <v>12262</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -2850,7 +2794,7 @@
         <v>11493</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>229</v>
       </c>
@@ -2861,7 +2805,7 @@
         <v>10235</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>231</v>
       </c>
@@ -2872,7 +2816,7 @@
         <v>9998</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>233</v>
       </c>
@@ -2883,7 +2827,7 @@
         <v>10620</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>235</v>
       </c>
@@ -2894,7 +2838,7 @@
         <v>10687</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>237</v>
       </c>
@@ -2905,7 +2849,7 @@
         <v>10670</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -2916,7 +2860,7 @@
         <v>10653</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>241</v>
       </c>
@@ -2927,7 +2871,7 @@
         <v>10974</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>243</v>
       </c>
@@ -2938,7 +2882,7 @@
         <v>10896</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>245</v>
       </c>
@@ -2949,7 +2893,7 @@
         <v>11371</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>247</v>
       </c>
@@ -2960,7 +2904,7 @@
         <v>11517</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -2971,7 +2915,7 @@
         <v>12178</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -2982,7 +2926,7 @@
         <v>12453</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -2993,7 +2937,7 @@
         <v>11732</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>255</v>
       </c>
@@ -3004,7 +2948,7 @@
         <v>12161</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>257</v>
       </c>
@@ -3015,7 +2959,7 @@
         <v>12382</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>259</v>
       </c>
@@ -3026,7 +2970,7 @@
         <v>12389</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>261</v>
       </c>
@@ -3037,7 +2981,7 @@
         <v>12633</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>263</v>
       </c>
@@ -3048,7 +2992,7 @@
         <v>13384</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>265</v>
       </c>
@@ -3059,7 +3003,7 @@
         <v>14389</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -3070,7 +3014,7 @@
         <v>14615</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>269</v>
       </c>
@@ -3081,7 +3025,7 @@
         <v>13231</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>271</v>
       </c>
@@ -3092,7 +3036,7 @@
         <v>13929</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>273</v>
       </c>
@@ -3103,7 +3047,7 @@
         <v>14290</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -3114,7 +3058,7 @@
         <v>13742</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>277</v>
       </c>
@@ -3125,7 +3069,7 @@
         <v>12890</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>279</v>
       </c>
@@ -3136,7 +3080,7 @@
         <v>12874</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -3147,7 +3091,7 @@
         <v>13527</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>283</v>
       </c>
@@ -3158,7 +3102,7 @@
         <v>13948</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -3166,7 +3110,7 @@
         <v>286</v>
       </c>
       <c r="C143">
-        <v>13921</v>
+        <v>14036</v>
       </c>
     </row>
   </sheetData>
@@ -3177,163 +3121,163 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D83"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C2">
         <v>56.55</v>
       </c>
       <c r="D2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2019</v>
       </c>
       <c r="B3" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C3">
         <v>61.31</v>
       </c>
       <c r="D3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" s="7">
+        <v>295</v>
+      </c>
+      <c r="C4" s="3">
         <v>63.6</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C5">
         <v>68.31</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2019</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C6">
         <v>68.069999999999993</v>
       </c>
       <c r="D6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2019</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C7" s="7">
+        <v>301</v>
+      </c>
+      <c r="C7" s="3">
         <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2019</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C8">
         <v>61.32</v>
       </c>
       <c r="D8" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2019</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C9">
         <v>57.27</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2019</v>
       </c>
       <c r="B10" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C10">
         <v>60.84</v>
       </c>
       <c r="D10" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
       <c r="B11" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C11">
         <v>59.82</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D11" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2019</v>
       </c>
@@ -3344,164 +3288,164 @@
         <v>63.26</v>
       </c>
       <c r="D12" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2019</v>
       </c>
       <c r="B13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C13">
         <v>67.180000000000007</v>
       </c>
       <c r="D13" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2020</v>
       </c>
       <c r="B14" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C14">
         <v>65.38</v>
       </c>
       <c r="D14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2020</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C15">
         <v>56.61</v>
       </c>
       <c r="D15" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C16">
         <v>34.229999999999997</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D16" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2020</v>
       </c>
       <c r="B17" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C17">
         <v>20.66</v>
       </c>
       <c r="D17" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2020</v>
       </c>
       <c r="B18" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C18">
         <v>25.67</v>
       </c>
       <c r="D18" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C19">
         <v>36.68</v>
       </c>
       <c r="D19" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2020</v>
       </c>
       <c r="B20" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C20">
         <v>40.64</v>
       </c>
       <c r="D20" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2020</v>
       </c>
       <c r="B21" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C21">
         <v>41.63</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2020</v>
       </c>
       <c r="B22" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C22">
         <v>37.43</v>
       </c>
       <c r="D22" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2020</v>
       </c>
       <c r="B23" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C23">
         <v>38.07</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -3512,164 +3456,164 @@
         <v>40.67</v>
       </c>
       <c r="D24" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2020</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C25">
         <v>47.78</v>
       </c>
       <c r="D25" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2021</v>
       </c>
       <c r="B26" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C26">
         <v>53.17</v>
       </c>
       <c r="D26" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2021</v>
       </c>
       <c r="B27" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C27">
         <v>60.36</v>
       </c>
       <c r="D27" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2021</v>
       </c>
       <c r="B28" t="s">
-        <v>306</v>
-      </c>
-      <c r="C28" s="7">
+        <v>295</v>
+      </c>
+      <c r="C28" s="3">
         <v>63.5</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2021</v>
       </c>
       <c r="B29" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C29">
         <v>61.96</v>
       </c>
       <c r="D29" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2021</v>
       </c>
       <c r="B30" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C30">
         <v>65.489999999999995</v>
       </c>
       <c r="D30" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2021</v>
       </c>
       <c r="B31" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C31">
         <v>70.23</v>
       </c>
       <c r="D31" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2021</v>
       </c>
       <c r="B32" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C32">
         <v>72.17</v>
       </c>
       <c r="D32" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2021</v>
       </c>
       <c r="B33" t="s">
-        <v>291</v>
-      </c>
-      <c r="C33" s="7">
+        <v>305</v>
+      </c>
+      <c r="C33" s="3">
         <v>67.8</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2021</v>
       </c>
       <c r="B34" t="s">
-        <v>292</v>
-      </c>
-      <c r="C34" s="7">
+        <v>307</v>
+      </c>
+      <c r="C34" s="3">
         <v>72.2</v>
       </c>
       <c r="D34" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2021</v>
       </c>
       <c r="B35" t="s">
-        <v>295</v>
-      </c>
-      <c r="C35" s="7">
+        <v>309</v>
+      </c>
+      <c r="C35" s="3">
         <v>81.8</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -3680,326 +3624,326 @@
         <v>80.13</v>
       </c>
       <c r="D36" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2021</v>
       </c>
       <c r="B37" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C37">
         <v>73.36</v>
       </c>
       <c r="D37" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2022</v>
       </c>
       <c r="B38" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C38">
         <v>85.89</v>
       </c>
       <c r="D38" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2022</v>
       </c>
       <c r="B39" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C39">
         <v>95.72</v>
       </c>
       <c r="D39" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2022</v>
       </c>
       <c r="B40" t="s">
-        <v>306</v>
-      </c>
-      <c r="C40" s="7">
+        <v>295</v>
+      </c>
+      <c r="C40" s="3">
         <v>113.5</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2022</v>
       </c>
       <c r="B41" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C41">
         <v>102.51</v>
       </c>
       <c r="D41" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2022</v>
       </c>
       <c r="B42" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C42">
         <v>109.61</v>
       </c>
       <c r="D42" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2022</v>
       </c>
       <c r="B43" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C43">
         <v>117.62</v>
       </c>
       <c r="D43" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2022</v>
       </c>
       <c r="B44" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C44">
         <v>106.73</v>
       </c>
       <c r="D44" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2022</v>
       </c>
       <c r="B45" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C45">
         <v>94.17</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D45" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2022</v>
       </c>
       <c r="B46" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C46">
         <v>86.07</v>
       </c>
       <c r="D46" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2022</v>
       </c>
       <c r="B47" t="s">
-        <v>295</v>
-      </c>
-      <c r="C47" s="7">
+        <v>309</v>
+      </c>
+      <c r="C47" s="3">
         <v>89.1</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2022</v>
       </c>
       <c r="B48" t="s">
         <v>311</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="3">
         <v>87.5</v>
       </c>
       <c r="D48" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2022</v>
       </c>
       <c r="B49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C49">
         <v>76.66</v>
       </c>
       <c r="D49" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2023</v>
       </c>
       <c r="B50" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C50">
         <v>78.540000000000006</v>
       </c>
       <c r="D50" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2023</v>
       </c>
       <c r="B51" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C51">
         <v>79.48</v>
       </c>
       <c r="D51" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2023</v>
       </c>
       <c r="B52" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C52">
         <v>74.59</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D52" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2023</v>
       </c>
       <c r="B53" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C53">
         <v>79.34</v>
       </c>
       <c r="D53" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2023</v>
       </c>
       <c r="B54" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C54">
         <v>70.12</v>
       </c>
       <c r="D54" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2023</v>
       </c>
       <c r="B55" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C55">
         <v>69.36</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2023</v>
       </c>
       <c r="B56" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2023</v>
       </c>
       <c r="B57" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C57">
         <v>82.59</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D57" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2023</v>
       </c>
       <c r="B58" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C58">
         <v>90.17</v>
       </c>
       <c r="D58" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2023</v>
       </c>
       <c r="B59" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C59">
         <v>86.72</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D59" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2023</v>
       </c>
@@ -4010,164 +3954,164 @@
         <v>79.63</v>
       </c>
       <c r="D60" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2023</v>
       </c>
       <c r="B61" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C61">
         <v>75.510000000000005</v>
       </c>
       <c r="D61" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2024</v>
       </c>
       <c r="B62" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C62">
         <v>77.12</v>
       </c>
       <c r="D62" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2024</v>
       </c>
       <c r="B63" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C63">
         <v>80.09</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D63" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2024</v>
       </c>
       <c r="B64" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C64">
         <v>83.78</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D64" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2024</v>
       </c>
       <c r="B65" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C65">
         <v>87.61</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D65" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2024</v>
       </c>
       <c r="B66" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C66">
         <v>79.78</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D66" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2024</v>
       </c>
       <c r="B67" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C67">
         <v>79.31</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D67" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2024</v>
       </c>
       <c r="B68" t="s">
-        <v>310</v>
-      </c>
-      <c r="C68" s="7">
+        <v>303</v>
+      </c>
+      <c r="C68" s="3">
         <v>82</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D68" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2024</v>
       </c>
       <c r="B69" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C69">
         <v>78.510000000000005</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D69" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2024</v>
       </c>
       <c r="B70" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C70">
         <v>72.540000000000006</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2024</v>
       </c>
       <c r="B71" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C71">
         <v>73.53</v>
       </c>
-      <c r="D71" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D71" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2024</v>
       </c>
@@ -4178,209 +4122,208 @@
         <v>71.83</v>
       </c>
       <c r="D72" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2024</v>
       </c>
       <c r="B73" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C73">
         <v>71.61</v>
       </c>
       <c r="D73" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2025</v>
       </c>
       <c r="B74" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="C74">
         <v>76.81</v>
       </c>
       <c r="D74" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2025</v>
       </c>
       <c r="B75" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C75">
         <v>74.290000000000006</v>
       </c>
       <c r="D75" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2025</v>
       </c>
       <c r="B76" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C76">
         <v>71.11</v>
       </c>
       <c r="D76" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2025</v>
       </c>
       <c r="B77" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C77">
         <v>65.290000000000006</v>
       </c>
       <c r="D77" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2025</v>
       </c>
       <c r="B78" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C78">
         <v>62.75</v>
       </c>
       <c r="D78" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2025</v>
       </c>
       <c r="B79" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C79">
         <v>69.33</v>
       </c>
       <c r="D79" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2025</v>
       </c>
       <c r="B80" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C80">
         <v>68.59</v>
       </c>
       <c r="D80" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2025</v>
       </c>
       <c r="B81" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C81">
         <v>66.069999999999993</v>
       </c>
       <c r="D81" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2025</v>
       </c>
       <c r="B82" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="C82" t="s">
-        <v>293</v>
+        <v>355</v>
       </c>
       <c r="D82" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2025</v>
       </c>
       <c r="B83" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C83" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="D83" t="s">
-        <v>297</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J129"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J130"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C1" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B2">
         <v>2015</v>
@@ -4410,9 +4353,9 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B3">
         <v>2015</v>
@@ -4442,9 +4385,9 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B4">
         <v>2015</v>
@@ -4474,9 +4417,9 @@
         <v>47.92</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B5">
         <v>2015</v>
@@ -4506,9 +4449,9 @@
         <v>50.79</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B6">
         <v>2015</v>
@@ -4538,9 +4481,9 @@
         <v>50.06</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B7">
         <v>2015</v>
@@ -4570,9 +4513,9 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B8">
         <v>2015</v>
@@ -4602,9 +4545,9 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B9">
         <v>2015</v>
@@ -4634,7 +4577,7 @@
         <v>48.82</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>311</v>
       </c>
@@ -4666,9 +4609,9 @@
         <v>48.84</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B11">
         <v>2015</v>
@@ -4698,9 +4641,9 @@
         <v>50.92</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B12">
         <v>2016</v>
@@ -4730,9 +4673,9 @@
         <v>47.64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B13">
         <v>2016</v>
@@ -4762,9 +4705,9 @@
         <v>50.38</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B14">
         <v>2016</v>
@@ -4794,9 +4737,9 @@
         <v>50.01</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B15">
         <v>2016</v>
@@ -4826,9 +4769,9 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B16">
         <v>2016</v>
@@ -4858,9 +4801,9 @@
         <v>50.62</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B17">
         <v>2016</v>
@@ -4890,9 +4833,9 @@
         <v>50.32</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B18">
         <v>2016</v>
@@ -4922,9 +4865,9 @@
         <v>49.62</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B19">
         <v>2016</v>
@@ -4954,9 +4897,9 @@
         <v>51.24</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B20">
         <v>2016</v>
@@ -4986,9 +4929,9 @@
         <v>49.94</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B21">
         <v>2016</v>
@@ -5018,7 +4961,7 @@
         <v>49.07</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>311</v>
       </c>
@@ -5050,9 +4993,9 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B23">
         <v>2016</v>
@@ -5082,9 +5025,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B24">
         <v>2017</v>
@@ -5114,9 +5057,9 @@
         <v>49.76</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B25">
         <v>2017</v>
@@ -5146,9 +5089,9 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B26">
         <v>2017</v>
@@ -5178,9 +5121,9 @@
         <v>51.71</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B27">
         <v>2017</v>
@@ -5210,9 +5153,9 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B28">
         <v>2017</v>
@@ -5242,9 +5185,9 @@
         <v>52.56</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B29">
         <v>2017</v>
@@ -5274,9 +5217,9 @@
         <v>53.34</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B30">
         <v>2017</v>
@@ -5306,9 +5249,9 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B31">
         <v>2017</v>
@@ -5338,9 +5281,9 @@
         <v>51.76</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B32">
         <v>2017</v>
@@ -5370,9 +5313,9 @@
         <v>53.05</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B33">
         <v>2017</v>
@@ -5402,7 +5345,7 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>311</v>
       </c>
@@ -5434,9 +5377,9 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35">
         <v>2017</v>
@@ -5466,9 +5409,9 @@
         <v>51.65</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B36">
         <v>2018</v>
@@ -5498,9 +5441,9 @@
         <v>50.67</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B37">
         <v>2018</v>
@@ -5530,9 +5473,9 @@
         <v>51.44</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B38">
         <v>2018</v>
@@ -5562,9 +5505,9 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B39">
         <v>2018</v>
@@ -5594,9 +5537,9 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B40">
         <v>2018</v>
@@ -5626,9 +5569,9 @@
         <v>52.54</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B41">
         <v>2018</v>
@@ -5658,9 +5601,9 @@
         <v>52.92</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B42">
         <v>2018</v>
@@ -5690,9 +5633,9 @@
         <v>52.68</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B43">
         <v>2018</v>
@@ -5722,9 +5665,9 @@
         <v>52.39</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B44">
         <v>2018</v>
@@ -5754,9 +5697,9 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B45">
         <v>2018</v>
@@ -5786,7 +5729,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>311</v>
       </c>
@@ -5818,9 +5761,9 @@
         <v>52.33</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B47">
         <v>2018</v>
@@ -5850,9 +5793,9 @@
         <v>53.01</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B48">
         <v>2019</v>
@@ -5882,9 +5825,9 @@
         <v>51.36</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B49">
         <v>2019</v>
@@ -5914,9 +5857,9 @@
         <v>52.02</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B50">
         <v>2019</v>
@@ -5946,9 +5889,9 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B51">
         <v>2019</v>
@@ -5978,9 +5921,9 @@
         <v>52.61</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B52">
         <v>2019</v>
@@ -6010,9 +5953,9 @@
         <v>53.23</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B53">
         <v>2019</v>
@@ -6042,9 +5985,9 @@
         <v>53.51</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B54">
         <v>2019</v>
@@ -6074,9 +6017,9 @@
         <v>53.47</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B55">
         <v>2019</v>
@@ -6106,9 +6049,9 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B56">
         <v>2019</v>
@@ -6138,9 +6081,9 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B57">
         <v>2019</v>
@@ -6170,7 +6113,7 @@
         <v>52.49</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>311</v>
       </c>
@@ -6202,9 +6145,9 @@
         <v>53.19</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B59">
         <v>2019</v>
@@ -6234,9 +6177,9 @@
         <v>53.74</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B60">
         <v>2020</v>
@@ -6266,9 +6209,9 @@
         <v>47.69</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B61">
         <v>2020</v>
@@ -6298,9 +6241,9 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B62">
         <v>2020</v>
@@ -6330,9 +6273,9 @@
         <v>47.63</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B63">
         <v>2020</v>
@@ -6362,9 +6305,9 @@
         <v>48.26</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B64">
         <v>2020</v>
@@ -6394,9 +6337,9 @@
         <v>48.86</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B65">
         <v>2020</v>
@@ -6426,9 +6369,9 @@
         <v>49.34</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B66">
         <v>2020</v>
@@ -6458,9 +6401,9 @@
         <v>49.54</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B67">
         <v>2020</v>
@@ -6490,9 +6433,9 @@
         <v>49.53</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B68">
         <v>2020</v>
@@ -6522,9 +6465,9 @@
         <v>50.15</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B69">
         <v>2020</v>
@@ -6554,7 +6497,7 @@
         <v>49.18</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>311</v>
       </c>
@@ -6586,9 +6529,9 @@
         <v>49.89</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B71">
         <v>2020</v>
@@ -6618,9 +6561,9 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B72">
         <v>2021</v>
@@ -6650,9 +6593,9 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B73">
         <v>2021</v>
@@ -6682,9 +6625,9 @@
         <v>51.74</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B74">
         <v>2021</v>
@@ -6714,9 +6657,9 @@
         <v>51.55</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B75">
         <v>2021</v>
@@ -6746,9 +6689,9 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B76">
         <v>2021</v>
@@ -6778,9 +6721,9 @@
         <v>52.34</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B77">
         <v>2021</v>
@@ -6810,9 +6753,9 @@
         <v>52.86</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B78">
         <v>2021</v>
@@ -6842,9 +6785,9 @@
         <v>52.47</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B79">
         <v>2021</v>
@@ -6874,9 +6817,9 @@
         <v>52.14</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B80">
         <v>2021</v>
@@ -6906,9 +6849,9 @@
         <v>52.76</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B81">
         <v>2021</v>
@@ -6938,7 +6881,7 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>311</v>
       </c>
@@ -6970,9 +6913,9 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B83">
         <v>2021</v>
@@ -7002,9 +6945,9 @@
         <v>52.94</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B84">
         <v>2022</v>
@@ -7034,9 +6977,9 @@
         <v>52.69</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B85">
         <v>2022</v>
@@ -7066,9 +7009,9 @@
         <v>53.79</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B86">
         <v>2022</v>
@@ -7098,9 +7041,9 @@
         <v>53.02</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B87">
         <v>2022</v>
@@ -7130,9 +7073,9 @@
         <v>53.36</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B88">
         <v>2022</v>
@@ -7162,9 +7105,9 @@
         <v>54.18</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B89">
         <v>2022</v>
@@ -7194,9 +7137,9 @@
         <v>54.79</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B90">
         <v>2022</v>
@@ -7226,9 +7169,9 @@
         <v>54.42</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B91">
         <v>2022</v>
@@ -7258,9 +7201,9 @@
         <v>54.16</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B92">
         <v>2022</v>
@@ -7290,9 +7233,9 @@
         <v>54.83</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B93">
         <v>2022</v>
@@ -7322,7 +7265,7 @@
         <v>53.72</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>311</v>
       </c>
@@ -7354,9 +7297,9 @@
         <v>54.29</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B95">
         <v>2022</v>
@@ -7386,9 +7329,9 @@
         <v>54.92</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B96">
         <v>2023</v>
@@ -7418,9 +7361,9 @@
         <v>54.54</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B97">
         <v>2023</v>
@@ -7450,9 +7393,9 @@
         <v>55.95</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B98">
         <v>2023</v>
@@ -7482,9 +7425,9 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B99">
         <v>2023</v>
@@ -7514,9 +7457,9 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B100">
         <v>2023</v>
@@ -7546,9 +7489,9 @@
         <v>56.58</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B101">
         <v>2023</v>
@@ -7578,9 +7521,9 @@
         <v>57.11</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B102">
         <v>2023</v>
@@ -7610,9 +7553,9 @@
         <v>56.68</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B103">
         <v>2023</v>
@@ -7642,9 +7585,9 @@
         <v>56.31</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B104">
         <v>2023</v>
@@ -7674,9 +7617,9 @@
         <v>56.97</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B105">
         <v>2023</v>
@@ -7706,7 +7649,7 @@
         <v>55.84</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>311</v>
       </c>
@@ -7738,9 +7681,9 @@
         <v>56.61</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B107">
         <v>2023</v>
@@ -7770,9 +7713,9 @@
         <v>57.23</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B108">
         <v>2024</v>
@@ -7802,9 +7745,9 @@
         <v>56.38</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B109">
         <v>2024</v>
@@ -7834,9 +7777,9 @@
         <v>57.81</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B110">
         <v>2024</v>
@@ -7866,9 +7809,9 @@
         <v>57.07</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B111">
         <v>2024</v>
@@ -7898,9 +7841,9 @@
         <v>56.86</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B112">
         <v>2024</v>
@@ -7930,9 +7873,9 @@
         <v>57.24</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B113">
         <v>2024</v>
@@ -7962,9 +7905,9 @@
         <v>57.89</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B114">
         <v>2024</v>
@@ -7994,9 +7937,9 @@
         <v>57.48</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B115">
         <v>2024</v>
@@ -8026,9 +7969,9 @@
         <v>56.77</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B116">
         <v>2024</v>
@@ -8058,9 +8001,9 @@
         <v>57.38</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B117">
         <v>2024</v>
@@ -8090,7 +8033,7 @@
         <v>56.28</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>311</v>
       </c>
@@ -8122,9 +8065,9 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B119">
         <v>2024</v>
@@ -8154,9 +8097,9 @@
         <v>58.28</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B120">
         <v>2025</v>
@@ -8186,9 +8129,9 @@
         <v>56.88</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B121">
         <v>2025</v>
@@ -8218,9 +8161,9 @@
         <v>57.79</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B122">
         <v>2025</v>
@@ -8250,9 +8193,9 @@
         <v>57.49</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B123">
         <v>2025</v>
@@ -8282,9 +8225,9 @@
         <v>57.88</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B124">
         <v>2025</v>
@@ -8314,9 +8257,9 @@
         <v>58.54</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B125">
         <v>2025</v>
@@ -8346,9 +8289,9 @@
         <v>59.18</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B126">
         <v>2025</v>
@@ -8378,9 +8321,9 @@
         <v>58.65</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B127">
         <v>2025</v>
@@ -8410,9 +8353,9 @@
         <v>58.25</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B128">
         <v>2025</v>
@@ -8442,9 +8385,9 @@
         <v>59.04</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B129">
         <v>2025</v>
@@ -8472,6 +8415,38 @@
       </c>
       <c r="J129">
         <v>57.92</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>311</v>
+      </c>
+      <c r="B130">
+        <v>2025</v>
+      </c>
+      <c r="C130">
+        <v>107.52</v>
+      </c>
+      <c r="D130">
+        <v>33.630000000000003</v>
+      </c>
+      <c r="E130">
+        <v>73.89</v>
+      </c>
+      <c r="F130">
+        <v>80.03</v>
+      </c>
+      <c r="G130">
+        <v>27.49</v>
+      </c>
+      <c r="H130">
+        <v>104.8</v>
+      </c>
+      <c r="I130">
+        <v>45.78</v>
+      </c>
+      <c r="J130">
+        <v>59.02</v>
       </c>
     </row>
   </sheetData>
@@ -8481,2546 +8456,2798 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B321"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B348"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
         <v>45474</v>
       </c>
       <c r="B2">
         <v>13000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
         <v>45475</v>
       </c>
       <c r="B3">
         <v>13185</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
         <v>45476</v>
       </c>
       <c r="B4">
         <v>13170</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
         <v>45477</v>
       </c>
       <c r="B5">
         <v>13225</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>45478</v>
       </c>
       <c r="B6">
         <v>13200</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
         <v>45481</v>
       </c>
       <c r="B7">
         <v>13175</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>45482</v>
       </c>
       <c r="B8">
         <v>12888</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
         <v>45483</v>
       </c>
       <c r="B9">
         <v>12638</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
         <v>45484</v>
       </c>
       <c r="B10">
         <v>12718</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
         <v>45485</v>
       </c>
       <c r="B11">
         <v>12729</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
         <v>45488</v>
       </c>
       <c r="B12">
         <v>12640</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
         <v>45489</v>
       </c>
       <c r="B13">
         <v>12723</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
         <v>45490</v>
       </c>
       <c r="B14">
         <v>12738</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
         <v>45491</v>
       </c>
       <c r="B15">
         <v>12740</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
         <v>45492</v>
       </c>
       <c r="B16">
         <v>12725</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
         <v>45495</v>
       </c>
       <c r="B17">
         <v>12810</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
         <v>45496</v>
       </c>
       <c r="B18">
         <v>12804</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
         <v>45497</v>
       </c>
       <c r="B19">
         <v>12757</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
         <v>45498</v>
       </c>
       <c r="B20">
         <v>12775</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
         <v>45499</v>
       </c>
       <c r="B21">
         <v>12965</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
         <v>45502</v>
       </c>
       <c r="B22">
         <v>13000</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
         <v>45503</v>
       </c>
       <c r="B23">
         <v>13050</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
         <v>45504</v>
       </c>
       <c r="B24">
         <v>13036</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
         <v>45505</v>
       </c>
       <c r="B25">
         <v>13040</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
         <v>45506</v>
       </c>
       <c r="B26">
         <v>13105</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
         <v>45509</v>
       </c>
       <c r="B27">
         <v>13209</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
         <v>45510</v>
       </c>
       <c r="B28">
         <v>13119</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
         <v>45511</v>
       </c>
       <c r="B29">
         <v>13054</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
         <v>45512</v>
       </c>
       <c r="B30">
         <v>12939</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
         <v>45513</v>
       </c>
       <c r="B31">
         <v>12918</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
         <v>45516</v>
       </c>
       <c r="B32">
         <v>12830</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
         <v>45517</v>
       </c>
       <c r="B33">
         <v>12782</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
         <v>45518</v>
       </c>
       <c r="B34">
         <v>12677</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
         <v>45519</v>
       </c>
       <c r="B35">
         <v>12520</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="5">
         <v>45520</v>
       </c>
       <c r="B36">
         <v>12588</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="5">
         <v>45523</v>
       </c>
       <c r="B37">
         <v>12625</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="5">
         <v>45524</v>
       </c>
       <c r="B38">
         <v>12675</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="5">
         <v>45525</v>
       </c>
       <c r="B39">
         <v>12745</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="5">
         <v>45526</v>
       </c>
       <c r="B40">
         <v>12868</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="5">
         <v>45527</v>
       </c>
       <c r="B41">
         <v>12959</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="5">
         <v>45530</v>
       </c>
       <c r="B42">
         <v>13089</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="5">
         <v>45531</v>
       </c>
       <c r="B43">
         <v>13233</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="5">
         <v>45532</v>
       </c>
       <c r="B44">
         <v>13235</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="5">
         <v>45533</v>
       </c>
       <c r="B45">
         <v>13155</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="5">
         <v>45534</v>
       </c>
       <c r="B46">
         <v>13328</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="5">
         <v>45537</v>
       </c>
       <c r="B47">
         <v>13242</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="5">
         <v>45538</v>
       </c>
       <c r="B48">
         <v>13342</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="5">
         <v>45539</v>
       </c>
       <c r="B49">
         <v>13212</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="5">
         <v>45540</v>
       </c>
       <c r="B50">
         <v>13131</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="5">
         <v>45541</v>
       </c>
       <c r="B51">
         <v>13100</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="5">
         <v>45544</v>
       </c>
       <c r="B52">
         <v>13058</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="5">
         <v>45545</v>
       </c>
       <c r="B53">
         <v>13089</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="5">
         <v>45546</v>
       </c>
       <c r="B54">
         <v>13118</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="5">
         <v>45547</v>
       </c>
       <c r="B55">
         <v>13070</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="5">
         <v>45548</v>
       </c>
       <c r="B56">
         <v>13035</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="5">
         <v>45552</v>
       </c>
       <c r="B57">
         <v>12925</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="5">
         <v>45553</v>
       </c>
       <c r="B58">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="5">
         <v>45554</v>
       </c>
       <c r="B59">
         <v>13358</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="5">
         <v>45555</v>
       </c>
       <c r="B60">
         <v>13407</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="5">
         <v>45558</v>
       </c>
       <c r="B61">
         <v>13640</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="5">
         <v>45559</v>
       </c>
       <c r="B62">
         <v>13570</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="5">
         <v>45560</v>
       </c>
       <c r="B63">
         <v>13759</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="5">
         <v>45561</v>
       </c>
       <c r="B64">
         <v>13928</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="5">
         <v>45562</v>
       </c>
       <c r="B65">
         <v>14004</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="5">
         <v>45565</v>
       </c>
       <c r="B66">
         <v>13978</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="5">
         <v>45566</v>
       </c>
       <c r="B67">
         <v>14106</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="5">
         <v>45567</v>
       </c>
       <c r="B68">
         <v>14027</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="5">
         <v>45568</v>
       </c>
       <c r="B69">
         <v>14138</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="5">
         <v>45569</v>
       </c>
       <c r="B70">
         <v>14322</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="5">
         <v>45572</v>
       </c>
       <c r="B71">
         <v>14242</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="5">
         <v>45573</v>
       </c>
       <c r="B72">
         <v>14040</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="5">
         <v>45574</v>
       </c>
       <c r="B73">
         <v>14078</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="5">
         <v>45575</v>
       </c>
       <c r="B74">
         <v>14029</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="5">
         <v>45576</v>
       </c>
       <c r="B75">
         <v>14262</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="5">
         <v>45579</v>
       </c>
       <c r="B76">
         <v>14135</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="5">
         <v>45580</v>
       </c>
       <c r="B77">
         <v>13977</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="5">
         <v>45581</v>
       </c>
       <c r="B78">
         <v>14111</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="5">
         <v>45582</v>
       </c>
       <c r="B79">
         <v>14038</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="5">
         <v>45583</v>
       </c>
       <c r="B80">
         <v>14000</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="5">
         <v>45586</v>
       </c>
       <c r="B81">
         <v>14020</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="5">
         <v>45587</v>
       </c>
       <c r="B82">
         <v>14183</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="5">
         <v>45588</v>
       </c>
       <c r="B83">
         <v>14337</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="5">
         <v>45589</v>
       </c>
       <c r="B84">
         <v>14507</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="5">
         <v>45590</v>
       </c>
       <c r="B85">
         <v>14721</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="5">
         <v>45593</v>
       </c>
       <c r="B86">
         <v>14685</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="5">
         <v>45594</v>
       </c>
       <c r="B87">
         <v>14750</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="5">
         <v>45595</v>
       </c>
       <c r="B88">
         <v>14810</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="5">
         <v>45596</v>
       </c>
       <c r="B89">
         <v>14888</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="5">
         <v>45597</v>
       </c>
       <c r="B90">
         <v>15118</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="5">
         <v>45600</v>
       </c>
       <c r="B91">
         <v>15350</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="1">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="5">
         <v>45601</v>
       </c>
       <c r="B92">
         <v>15310</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="5">
         <v>45602</v>
       </c>
       <c r="B93">
         <v>15330</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="5">
         <v>45603</v>
       </c>
       <c r="B94">
         <v>15430</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="5">
         <v>45604</v>
       </c>
       <c r="B95">
         <v>15544</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="5">
         <v>45607</v>
       </c>
       <c r="B96">
         <v>15788</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="5">
         <v>45608</v>
       </c>
       <c r="B97">
         <v>15738</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="5">
         <v>45609</v>
       </c>
       <c r="B98">
         <v>15367</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="5">
         <v>45610</v>
       </c>
       <c r="B99">
         <v>15254</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="5">
         <v>45611</v>
       </c>
       <c r="B100">
         <v>15350</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="5">
         <v>45614</v>
       </c>
       <c r="B101">
         <v>15255</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="5">
         <v>45615</v>
       </c>
       <c r="B102">
         <v>15365</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="5">
         <v>45616</v>
       </c>
       <c r="B103">
         <v>15275</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="5">
         <v>45617</v>
       </c>
       <c r="B104">
         <v>15000</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="5">
         <v>45618</v>
       </c>
       <c r="B105">
         <v>14813</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="5">
         <v>45621</v>
       </c>
       <c r="B106">
         <v>14964</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="5">
         <v>45622</v>
       </c>
       <c r="B107">
         <v>15165</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="5">
         <v>45624</v>
       </c>
       <c r="B108">
         <v>15245</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="5">
         <v>45625</v>
       </c>
       <c r="B109">
         <v>15584</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="5">
         <v>45628</v>
       </c>
       <c r="B110">
         <v>15656</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" s="1">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="5">
         <v>45629</v>
       </c>
       <c r="B111">
         <v>15788</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" s="1">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="5">
         <v>45630</v>
       </c>
       <c r="B112">
         <v>15900</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="5">
         <v>45631</v>
       </c>
       <c r="B113">
         <v>15976</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" s="1">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="5">
         <v>45632</v>
       </c>
       <c r="B114">
         <v>16000</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" s="1">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="5">
         <v>45635</v>
       </c>
       <c r="B115">
         <v>15940</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" s="1">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="5">
         <v>45636</v>
       </c>
       <c r="B116">
         <v>15760</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="1">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="5">
         <v>45637</v>
       </c>
       <c r="B117">
         <v>15675</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" s="1">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="5">
         <v>45638</v>
       </c>
       <c r="B118">
         <v>15602</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="5">
         <v>45639</v>
       </c>
       <c r="B119">
         <v>15553</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" s="1">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="5">
         <v>45642</v>
       </c>
       <c r="B120">
         <v>15589</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="5">
         <v>45643</v>
       </c>
       <c r="B121">
         <v>15327</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="5">
         <v>45644</v>
       </c>
       <c r="B122">
         <v>14919</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="1">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="5">
         <v>45645</v>
       </c>
       <c r="B123">
         <v>14646</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" s="1">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="5">
         <v>45646</v>
       </c>
       <c r="B124">
         <v>14684</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" s="5">
         <v>45649</v>
       </c>
       <c r="B125">
         <v>14726</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" s="5">
         <v>45650</v>
       </c>
       <c r="B126">
         <v>14858</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" s="1">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" s="5">
         <v>45660</v>
       </c>
       <c r="B127">
         <v>14454</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" s="5">
         <v>45663</v>
       </c>
       <c r="B128">
         <v>14253</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" s="5">
         <v>45664</v>
       </c>
       <c r="B129">
         <v>14157</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" s="5">
         <v>45665</v>
       </c>
       <c r="B130">
         <v>14069</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" s="5">
         <v>45666</v>
       </c>
       <c r="B131">
         <v>13852</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" s="5">
         <v>45667</v>
       </c>
       <c r="B132">
         <v>13895</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" s="5">
         <v>45670</v>
       </c>
       <c r="B133">
         <v>14206</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" s="5">
         <v>45671</v>
       </c>
       <c r="B134">
         <v>14188</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" s="1">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" s="5">
         <v>45672</v>
       </c>
       <c r="B135">
         <v>14000</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" s="1">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" s="5">
         <v>45673</v>
       </c>
       <c r="B136">
         <v>13712</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" s="5">
         <v>45674</v>
       </c>
       <c r="B137">
         <v>13585</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" s="5">
         <v>45677</v>
       </c>
       <c r="B138">
         <v>13725</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" s="5">
         <v>45678</v>
       </c>
       <c r="B139">
         <v>13816</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" s="1">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" s="5">
         <v>45679</v>
       </c>
       <c r="B140">
         <v>13670</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" s="1">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" s="5">
         <v>45680</v>
       </c>
       <c r="B141">
         <v>13533</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" s="1">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" s="5">
         <v>45681</v>
       </c>
       <c r="B142">
         <v>13605</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" s="5">
         <v>45687</v>
       </c>
       <c r="B143">
         <v>13750</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144" s="1">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" s="5">
         <v>45688</v>
       </c>
       <c r="B144">
         <v>13889</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="1">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" s="5">
         <v>45691</v>
       </c>
       <c r="B145">
         <v>14100</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="1">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" s="5">
         <v>45692</v>
       </c>
       <c r="B146">
         <v>14008</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A147" s="1">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" s="5">
         <v>45693</v>
       </c>
       <c r="B147">
         <v>14150</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" s="1">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" s="5">
         <v>45694</v>
       </c>
       <c r="B148">
         <v>14265</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149" s="1">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" s="5">
         <v>45695</v>
       </c>
       <c r="B149">
         <v>14500</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150" s="1">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" s="5">
         <v>45698</v>
       </c>
       <c r="B150">
         <v>14639</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" s="1">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" s="5">
         <v>45699</v>
       </c>
       <c r="B151">
         <v>14740</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" s="1">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" s="5">
         <v>45700</v>
       </c>
       <c r="B152">
         <v>15000</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="1">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" s="5">
         <v>45701</v>
       </c>
       <c r="B153">
         <v>14802</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154" s="1">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" s="5">
         <v>45702</v>
       </c>
       <c r="B154">
         <v>14888</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A155" s="1">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" s="5">
         <v>45705</v>
       </c>
       <c r="B155">
         <v>14850</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" s="5">
         <v>45706</v>
       </c>
       <c r="B156">
         <v>14900</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A157" s="1">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" s="5">
         <v>45707</v>
       </c>
       <c r="B157">
         <v>15140</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="1">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" s="5">
         <v>45708</v>
       </c>
       <c r="B158">
         <v>15275</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="1">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" s="5">
         <v>45709</v>
       </c>
       <c r="B159">
         <v>15425</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160" s="1">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" s="5">
         <v>45712</v>
       </c>
       <c r="B160">
         <v>15275</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="1">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" s="5">
         <v>45713</v>
       </c>
       <c r="B161">
         <v>15400</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="1">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" s="5">
         <v>45714</v>
       </c>
       <c r="B162">
         <v>15320</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="1">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" s="5">
         <v>45715</v>
       </c>
       <c r="B163">
         <v>15108</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" s="5">
         <v>45716</v>
       </c>
       <c r="B164">
         <v>15162</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="1">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165" s="5">
         <v>45719</v>
       </c>
       <c r="B165">
         <v>15000</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="1">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A166" s="5">
         <v>45720</v>
       </c>
       <c r="B166">
         <v>14740</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="1">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A167" s="5">
         <v>45721</v>
       </c>
       <c r="B167">
         <v>14800</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="1">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A168" s="5">
         <v>45722</v>
       </c>
       <c r="B168">
         <v>14933</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="1">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A169" s="5">
         <v>45723</v>
       </c>
       <c r="B169">
         <v>15135</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="1">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A170" s="5">
         <v>45726</v>
       </c>
       <c r="B170">
         <v>15105</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="1">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A171" s="5">
         <v>45727</v>
       </c>
       <c r="B171">
         <v>14980</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="1">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A172" s="5">
         <v>45728</v>
       </c>
       <c r="B172">
         <v>15075</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A173" s="1">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A173" s="5">
         <v>45729</v>
       </c>
       <c r="B173">
         <v>15150</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174" s="1">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A174" s="5">
         <v>45730</v>
       </c>
       <c r="B174">
         <v>15150</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="1">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A175" s="5">
         <v>45733</v>
       </c>
       <c r="B175">
         <v>15100</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="1">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A176" s="5">
         <v>45734</v>
       </c>
       <c r="B176">
         <v>15050</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="1">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A177" s="5">
         <v>45735</v>
       </c>
       <c r="B177">
         <v>15118</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="1">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A178" s="5">
         <v>45736</v>
       </c>
       <c r="B178">
         <v>15167</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="1">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A179" s="5">
         <v>45737</v>
       </c>
       <c r="B179">
         <v>14988</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="1">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A180" s="5">
         <v>45740</v>
       </c>
       <c r="B180">
         <v>14843</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="1">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A181" s="5">
         <v>45741</v>
       </c>
       <c r="B181">
         <v>14781</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="1">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A182" s="5">
         <v>45742</v>
       </c>
       <c r="B182">
         <v>14800</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="1">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A183" s="5">
         <v>45756</v>
       </c>
       <c r="B183">
         <v>14288</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="1">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A184" s="5">
         <v>45757</v>
       </c>
       <c r="B184">
         <v>14387</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="1">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A185" s="5">
         <v>45758</v>
       </c>
       <c r="B185">
         <v>14325</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="1">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A186" s="5">
         <v>45761</v>
       </c>
       <c r="B186">
         <v>14260</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="1">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A187" s="5">
         <v>45762</v>
       </c>
       <c r="B187">
         <v>14177</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="1">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A188" s="5">
         <v>45763</v>
       </c>
       <c r="B188">
         <v>14100</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="1">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A189" s="5">
         <v>45764</v>
       </c>
       <c r="B189">
         <v>14225</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="1">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A190" s="5">
         <v>45768</v>
       </c>
       <c r="B190">
         <v>14001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="1">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A191" s="5">
         <v>45769</v>
       </c>
       <c r="B191">
         <v>14401</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="1">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A192" s="5">
         <v>45770</v>
       </c>
       <c r="B192">
         <v>14501</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="1">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A193" s="5">
         <v>45771</v>
       </c>
       <c r="B193">
         <v>14488</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="1">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A194" s="5">
         <v>45772</v>
       </c>
       <c r="B194">
         <v>14470</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="1">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A195" s="5">
         <v>45775</v>
       </c>
       <c r="B195">
         <v>14006</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" s="1">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A196" s="5">
         <v>45776</v>
       </c>
       <c r="B196">
         <v>14000</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" s="1">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A197" s="5">
         <v>45777</v>
       </c>
       <c r="B197">
         <v>13900</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="1">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A198" s="5">
         <v>45779</v>
       </c>
       <c r="B198">
         <v>13891</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="1">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A199" s="5">
         <v>45782</v>
       </c>
       <c r="B199">
         <v>13500</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="1">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A200" s="5">
         <v>45783</v>
       </c>
       <c r="B200">
         <v>13316</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" s="1">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A201" s="5">
         <v>45784</v>
       </c>
       <c r="B201">
         <v>13130</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="1">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A202" s="5">
         <v>45785</v>
       </c>
       <c r="B202">
         <v>13100</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" s="1">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A203" s="5">
         <v>45786</v>
       </c>
       <c r="B203">
         <v>13150</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" s="1">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A204" s="5">
         <v>45791</v>
       </c>
       <c r="B204">
         <v>13422</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="1">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A205" s="5">
         <v>45792</v>
       </c>
       <c r="B205">
         <v>13373</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" s="1">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A206" s="5">
         <v>45793</v>
       </c>
       <c r="B206">
         <v>13211</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="1">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A207" s="5">
         <v>45796</v>
       </c>
       <c r="B207">
         <v>13256</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208" s="1">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A208" s="5">
         <v>45797</v>
       </c>
       <c r="B208">
         <v>13350</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A209" s="1">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A209" s="5">
         <v>45798</v>
       </c>
       <c r="B209">
         <v>13400</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A210" s="1">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A210" s="5">
         <v>45799</v>
       </c>
       <c r="B210">
         <v>13350</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211" s="1">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A211" s="5">
         <v>45800</v>
       </c>
       <c r="B211">
         <v>13361</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A212" s="1">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A212" s="5">
         <v>45803</v>
       </c>
       <c r="B212">
         <v>13125</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A213" s="1">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A213" s="5">
         <v>45804</v>
       </c>
       <c r="B213">
         <v>13180</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A214" s="1">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A214" s="5">
         <v>45805</v>
       </c>
       <c r="B214">
         <v>13315</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215" s="1">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A215" s="5">
         <v>45810</v>
       </c>
       <c r="B215">
         <v>13331</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A216" s="1">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A216" s="5">
         <v>45811</v>
       </c>
       <c r="B216">
         <v>13386</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A217" s="1">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A217" s="5">
         <v>45812</v>
       </c>
       <c r="B217">
         <v>13385</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A218" s="1">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A218" s="5">
         <v>45813</v>
       </c>
       <c r="B218">
         <v>13343</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A219" s="1">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A219" s="5">
         <v>45818</v>
       </c>
       <c r="B219">
         <v>13328</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A220" s="1">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A220" s="5">
         <v>45819</v>
       </c>
       <c r="B220">
         <v>13145</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A221" s="1">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A221" s="5">
         <v>45820</v>
       </c>
       <c r="B221">
         <v>13225</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A222" s="1">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A222" s="5">
         <v>45821</v>
       </c>
       <c r="B222">
         <v>13360</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A223" s="1">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A223" s="5">
         <v>45824</v>
       </c>
       <c r="B223">
         <v>13600</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A224" s="1">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A224" s="5">
         <v>45825</v>
       </c>
       <c r="B224">
         <v>13600</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A225" s="1">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A225" s="5">
         <v>45826</v>
       </c>
       <c r="B225">
         <v>13615</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A226" s="1">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A226" s="5">
         <v>45827</v>
       </c>
       <c r="B226">
         <v>13677</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A227" s="1">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A227" s="5">
         <v>45828</v>
       </c>
       <c r="B227">
         <v>13655</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A228" s="1">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A228" s="5">
         <v>45831</v>
       </c>
       <c r="B228">
         <v>13730</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A229" s="1">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A229" s="5">
         <v>45832</v>
       </c>
       <c r="B229">
         <v>13415</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A230" s="1">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A230" s="5">
         <v>45833</v>
       </c>
       <c r="B230">
         <v>13500</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A231" s="1">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A231" s="5">
         <v>45834</v>
       </c>
       <c r="B231">
         <v>13550</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A232" s="1">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A232" s="5">
         <v>45838</v>
       </c>
       <c r="B232">
         <v>13550</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A233" s="1">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A233" s="5">
         <v>45839</v>
       </c>
       <c r="B233">
         <v>13575</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A234" s="1">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A234" s="5">
         <v>45840</v>
       </c>
       <c r="B234">
         <v>13700</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A235" s="1">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A235" s="5">
         <v>45841</v>
       </c>
       <c r="B235">
         <v>13800</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A236" s="1">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A236" s="5">
         <v>45842</v>
       </c>
       <c r="B236">
         <v>13850</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A237" s="1">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A237" s="5">
         <v>45845</v>
       </c>
       <c r="B237">
         <v>13900</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A238" s="1">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A238" s="5">
         <v>45846</v>
       </c>
       <c r="B238">
         <v>13975</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A239" s="1">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A239" s="5">
         <v>45847</v>
       </c>
       <c r="B239">
         <v>14100</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A240" s="1">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A240" s="5">
         <v>45848</v>
       </c>
       <c r="B240">
         <v>14100</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A241" s="1">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A241" s="5">
         <v>45849</v>
       </c>
       <c r="B241">
         <v>14200</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A242" s="1">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A242" s="5">
         <v>45852</v>
       </c>
       <c r="B242">
         <v>14245</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A243" s="1">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A243" s="5">
         <v>45853</v>
       </c>
       <c r="B243">
         <v>14250</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A244" s="1">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A244" s="5">
         <v>45854</v>
       </c>
       <c r="B244">
         <v>14350</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A245" s="1">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A245" s="5">
         <v>45855</v>
       </c>
       <c r="B245">
         <v>14360</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A246" s="1">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A246" s="5">
         <v>45856</v>
       </c>
       <c r="B246">
         <v>14555</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A247" s="1">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A247" s="5">
         <v>45859</v>
       </c>
       <c r="B247">
         <v>14576</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A248" s="1">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A248" s="5">
         <v>45860</v>
       </c>
       <c r="B248">
         <v>14550</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A249" s="1">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A249" s="5">
         <v>45861</v>
       </c>
       <c r="B249">
         <v>14666</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A250" s="1">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A250" s="5">
         <v>45862</v>
       </c>
       <c r="B250">
         <v>14625</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A251" s="1">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A251" s="5">
         <v>45863</v>
       </c>
       <c r="B251">
         <v>14525</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A252" s="1">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A252" s="5">
         <v>45866</v>
       </c>
       <c r="B252">
         <v>14494</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A253" s="1">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A253" s="5">
         <v>45867</v>
       </c>
       <c r="B253">
         <v>14575</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A254" s="1">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A254" s="5">
         <v>45868</v>
       </c>
       <c r="B254">
         <v>14625</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A255" s="1">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A255" s="5">
         <v>45869</v>
       </c>
       <c r="B255">
         <v>14635</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A256" s="1">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A256" s="5">
         <v>45870</v>
       </c>
       <c r="B256">
         <v>14600</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A257" s="1">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A257" s="5">
         <v>45873</v>
       </c>
       <c r="B257">
         <v>14500</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A258" s="1">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A258" s="5">
         <v>45874</v>
       </c>
       <c r="B258">
         <v>14689</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A259" s="1">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A259" s="5">
         <v>45875</v>
       </c>
       <c r="B259">
         <v>14600</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A260" s="1">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A260" s="5">
         <v>45876</v>
       </c>
       <c r="B260">
         <v>14530</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A261" s="1">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A261" s="5">
         <v>45877</v>
       </c>
       <c r="B261">
         <v>14605</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A262" s="1">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A262" s="5">
         <v>45880</v>
       </c>
       <c r="B262">
         <v>14700</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A263" s="1">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A263" s="5">
         <v>45881</v>
       </c>
       <c r="B263">
         <v>14825</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A264" s="1">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A264" s="5">
         <v>45882</v>
       </c>
       <c r="B264">
         <v>14852</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A265" s="1">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A265" s="5">
         <v>45883</v>
       </c>
       <c r="B265">
         <v>14707</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A266" s="1">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A266" s="5">
         <v>45884</v>
       </c>
       <c r="B266">
         <v>14705</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A267" s="1">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A267" s="5">
         <v>45888</v>
       </c>
       <c r="B267">
         <v>14726</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A268" s="1">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A268" s="5">
         <v>45889</v>
       </c>
       <c r="B268">
         <v>14642</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A269" s="1">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A269" s="5">
         <v>45890</v>
       </c>
       <c r="B269">
         <v>14580</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A270" s="1">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A270" s="5">
         <v>45891</v>
       </c>
       <c r="B270">
         <v>14600</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A271" s="1">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A271" s="5">
         <v>45894</v>
       </c>
       <c r="B271">
         <v>14699</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A272" s="1">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A272" s="5">
         <v>45895</v>
       </c>
       <c r="B272">
         <v>14570</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A273" s="1">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A273" s="5">
         <v>45896</v>
       </c>
       <c r="B273">
         <v>14650</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A274" s="1">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A274" s="5">
         <v>45897</v>
       </c>
       <c r="B274">
         <v>14550</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A275" s="1">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A275" s="5">
         <v>45898</v>
       </c>
       <c r="B275">
         <v>14525</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A276" s="1">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A276" s="5">
         <v>45901</v>
       </c>
       <c r="B276">
         <v>14500</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A277" s="1">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A277" s="5">
         <v>45902</v>
       </c>
       <c r="B277">
         <v>14650</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A278" s="1">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A278" s="5">
         <v>45903</v>
       </c>
       <c r="B278">
         <v>14650</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A279" s="1">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A279" s="5">
         <v>45904</v>
       </c>
       <c r="B279">
         <v>14665</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A280" s="1">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A280" s="5">
         <v>45908</v>
       </c>
       <c r="B280">
         <v>14601</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A281" s="1">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A281" s="5">
         <v>45909</v>
       </c>
       <c r="B281">
         <v>14625</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A282" s="1">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A282" s="5">
         <v>45910</v>
       </c>
       <c r="B282">
         <v>14525</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A283" s="1">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A283" s="5">
         <v>45911</v>
       </c>
       <c r="B283">
         <v>14540</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A284" s="1">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A284" s="5">
         <v>45912</v>
       </c>
       <c r="B284">
         <v>14525</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A285" s="1">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A285" s="5">
         <v>45915</v>
       </c>
       <c r="B285">
         <v>14528</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A286" s="1">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A286" s="5">
         <v>45916</v>
       </c>
       <c r="B286">
         <v>14590</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A287" s="1">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A287" s="5">
         <v>45917</v>
       </c>
       <c r="B287">
         <v>14710</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A288" s="1">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A288" s="5">
         <v>45918</v>
       </c>
       <c r="B288">
         <v>14623</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A289" s="1">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A289" s="5">
         <v>45919</v>
       </c>
       <c r="B289">
         <v>14661</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A290" s="1">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A290" s="5">
         <v>45922</v>
       </c>
       <c r="B290">
         <v>14755</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A291" s="1">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A291" s="5">
         <v>45923</v>
       </c>
       <c r="B291">
         <v>14475</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A292" s="1">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A292" s="5">
         <v>45924</v>
       </c>
       <c r="B292">
         <v>14498</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A293" s="1">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A293" s="5">
         <v>45925</v>
       </c>
       <c r="B293">
         <v>14600</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A294" s="1">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A294" s="5">
         <v>45926</v>
       </c>
       <c r="B294">
         <v>14678</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A295" s="1">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A295" s="5">
         <v>45929</v>
       </c>
       <c r="B295">
         <v>14700</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A296" s="1">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A296" s="5">
         <v>45930</v>
       </c>
       <c r="B296">
         <v>14545</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A297" s="1">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A297" s="5">
         <v>45931</v>
       </c>
       <c r="B297">
         <v>14575</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A298" s="1">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A298" s="5">
         <v>45932</v>
       </c>
       <c r="B298">
         <v>14750</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A299" s="1">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A299" s="5">
         <v>45933</v>
       </c>
       <c r="B299">
         <v>14700</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A300" s="1">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A300" s="5">
         <v>45936</v>
       </c>
       <c r="B300">
         <v>14650</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A301" s="1">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A301" s="5">
         <v>45937</v>
       </c>
       <c r="B301">
         <v>14751</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A302" s="1">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A302" s="5">
         <v>45938</v>
       </c>
       <c r="B302">
         <v>14901</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A303" s="1">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A303" s="5">
         <v>45939</v>
       </c>
       <c r="B303">
         <v>14999</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A304" s="1">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A304" s="5">
         <v>45940</v>
       </c>
       <c r="B304">
         <v>14942</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A305" s="1">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A305" s="5">
         <v>45943</v>
       </c>
       <c r="B305">
         <v>14545</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A306" s="1">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A306" s="5">
         <v>45944</v>
       </c>
       <c r="B306">
         <v>14603</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A307" s="1">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A307" s="5">
         <v>45945</v>
       </c>
       <c r="B307">
         <v>14600</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A308" s="1">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A308" s="5">
         <v>45946</v>
       </c>
       <c r="B308">
         <v>14625</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A309" s="1">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A309" s="5">
         <v>45947</v>
       </c>
       <c r="B309">
         <v>14625</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A310" s="1">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A310" s="5">
         <v>45950</v>
       </c>
       <c r="B310">
         <v>14611</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A311" s="1">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A311" s="5">
         <v>45951</v>
       </c>
       <c r="B311">
         <v>14711</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A312" s="1">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A312" s="5">
         <v>45952</v>
       </c>
       <c r="B312">
         <v>14556</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A313" s="1">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A313" s="5">
         <v>45953</v>
       </c>
       <c r="B313">
         <v>15526</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A314" s="1">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A314" s="5">
         <v>45954</v>
       </c>
       <c r="B314">
         <v>14500</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A315" s="1"/>
-    </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A316" s="1"/>
-    </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A317" s="1"/>
-    </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A318" s="1"/>
-    </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A319" s="1"/>
-    </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A320" s="1"/>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A321" s="1"/>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A315" s="5">
+        <v>45957</v>
+      </c>
+      <c r="B315">
+        <v>15530</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A316" s="5">
+        <v>45958</v>
+      </c>
+      <c r="B316">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A317" s="5">
+        <v>45959</v>
+      </c>
+      <c r="B317">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A318" s="5">
+        <v>45960</v>
+      </c>
+      <c r="B318">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A319" s="5">
+        <v>45961</v>
+      </c>
+      <c r="B319">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A320" s="5">
+        <v>45962</v>
+      </c>
+      <c r="B320">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A321" s="5">
+        <v>45963</v>
+      </c>
+      <c r="B321">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A322" s="5">
+        <v>45964</v>
+      </c>
+      <c r="B322">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A323" s="5">
+        <v>45965</v>
+      </c>
+      <c r="B323">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A324" s="5">
+        <v>45966</v>
+      </c>
+      <c r="B324">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A325" s="5">
+        <v>45967</v>
+      </c>
+      <c r="B325">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A326" s="5">
+        <v>45968</v>
+      </c>
+      <c r="B326">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A327" s="5">
+        <v>45969</v>
+      </c>
+      <c r="B327">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A328" s="5">
+        <v>45970</v>
+      </c>
+      <c r="B328">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A329" s="5">
+        <v>45971</v>
+      </c>
+      <c r="B329">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A330" s="5">
+        <v>45972</v>
+      </c>
+      <c r="B330">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A331" s="5">
+        <v>45973</v>
+      </c>
+      <c r="B331">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A332" s="5">
+        <v>45974</v>
+      </c>
+      <c r="B332">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A333" s="5">
+        <v>45975</v>
+      </c>
+      <c r="B333">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A334" s="5">
+        <v>45976</v>
+      </c>
+      <c r="B334">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A335" s="5">
+        <v>45977</v>
+      </c>
+      <c r="B335">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A336" s="5">
+        <v>45978</v>
+      </c>
+      <c r="B336">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A337" s="5">
+        <v>45979</v>
+      </c>
+      <c r="B337">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A338" s="5">
+        <v>45980</v>
+      </c>
+      <c r="B338">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A339" s="5">
+        <v>45981</v>
+      </c>
+      <c r="B339">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A340" s="5">
+        <v>45982</v>
+      </c>
+      <c r="B340">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A341" s="5">
+        <v>45983</v>
+      </c>
+      <c r="B341">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A342" s="5">
+        <v>45984</v>
+      </c>
+      <c r="B342">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A343" s="5">
+        <v>45985</v>
+      </c>
+      <c r="B343">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A344" s="5">
+        <v>45986</v>
+      </c>
+      <c r="B344">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A345" s="5">
+        <v>45987</v>
+      </c>
+      <c r="B345">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A346" s="5">
+        <v>45988</v>
+      </c>
+      <c r="B346">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A347" s="5">
+        <v>45989</v>
+      </c>
+      <c r="B347">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A348" s="5">
+        <v>45990</v>
+      </c>
+      <c r="B348">
+        <v>14505</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/results/Terstruktur(Data Scrapping).xlsx
+++ b/src/results/Terstruktur(Data Scrapping).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pekerjaan\Dashboard-Pertamina-VeloCT\src\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\PEI\Dashboard-Pertamina-VeloCT\src\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76E9B2D-5D7A-4D6C-8651-FCB0631E8F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5991A09C-9D95-4F12-9D0B-3CF33808CC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="290" yWindow="1900" windowWidth="18910" windowHeight="9820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(Data)Biodesel" sheetId="1" r:id="rId1"/>
@@ -1137,8 +1137,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1221,7 +1221,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1233,7 +1233,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1538,9 +1538,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C143"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>10143</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>8794</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>8939</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>9343</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>9112</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>8954</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>8922</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>8770</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>7829</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>7494</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>6478</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>9456</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>9271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>9081</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>8189</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>7680</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>6686</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>6890</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>7039</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>6626</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>6954</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>7112</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>7687</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>8026</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>8891</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>8737</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>8402</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>7835</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>8483</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>9028</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>8262</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>8779</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9362</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>9493</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>9358</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>8815</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>8230</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>8302</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>7871</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>7965</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>8518</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>8490</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>8491</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>7962</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>103</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>8161</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>8356</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>8261</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>8140</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>111</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>7949</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>7294</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>7341</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>119</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>7227</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>125</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>7015</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>7403</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>7387</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>7348</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>6977</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>135</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>6970</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>7358</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>7157</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>7914</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>147</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>8706</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>9539</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>8933</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>8019</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>8352</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>6941</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>7321</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>161</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>7887</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>9003</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>9265</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>9329</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>169</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>171</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>9457</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>173</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>9579</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>9434</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>177</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>10131</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>179</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>10229</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>11034</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>9852</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>185</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>10635</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>11930</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>189</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>12022</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>191</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>12854</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>193</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>13746</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>195</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>13177</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>13867</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>199</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>14436</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>201</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>15559</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>203</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>15211</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>205</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>13033</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>207</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>11070</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>209</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>8047</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>211</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>10281</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>213</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>10787</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>11012</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>217</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>12039</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>219</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>11520</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>221</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>11233</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>223</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>11473</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>225</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>12262</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>11493</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>229</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>10235</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>231</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>9998</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>233</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>10620</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>235</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>10687</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>237</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>10670</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>10653</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>241</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>10974</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>243</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>10896</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>245</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>11371</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>247</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>11517</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>12178</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>12453</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>11732</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>255</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>12161</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>257</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>12382</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>259</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>12389</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>261</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>12633</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>263</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>13384</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>265</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>14389</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>14615</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>269</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>13231</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>271</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>13929</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>273</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>14290</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>13742</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>277</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>12890</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>279</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>12874</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>13527</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>283</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>13948</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -3121,9 +3121,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D83"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>287</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2019</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2019</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2019</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2019</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2019</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2019</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2019</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2019</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2020</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2020</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2020</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2020</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2020</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2020</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2020</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2020</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2021</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2021</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2021</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2021</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2021</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2021</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2021</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2021</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2021</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2021</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2022</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2022</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2022</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2022</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2022</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2022</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2022</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2022</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2022</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2022</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2022</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2022</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2023</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2023</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2023</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2023</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2023</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2023</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2023</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2023</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2023</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2023</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2023</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2023</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2024</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2024</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2024</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2024</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2024</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2024</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2024</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2024</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2024</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2024</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2024</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2024</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2025</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2025</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2025</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>2025</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2025</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>2025</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>2025</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2025</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2025</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>2025</v>
       </c>
@@ -4287,9 +4287,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J130"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>288</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>295</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>297</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>299</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>47.92</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>301</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>50.79</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>303</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>50.06</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>305</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>307</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>309</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>48.82</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>311</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>48.84</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>313</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>50.92</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>291</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>47.64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>293</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>50.38</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>295</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>50.01</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>297</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>299</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>50.62</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>301</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>50.32</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>303</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>49.62</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>305</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>51.24</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>307</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>49.94</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>309</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>49.07</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>311</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>313</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>291</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>49.76</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>293</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>295</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>51.71</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>297</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>299</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>52.56</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>301</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>53.34</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>303</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>305</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>51.76</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>307</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>53.05</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>309</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>311</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>313</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>51.65</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>291</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>50.67</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>293</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>51.44</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>295</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>297</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>299</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>52.54</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>301</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>52.92</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>303</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>52.68</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>305</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>52.39</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>307</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>309</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>311</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>52.33</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>313</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>53.01</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>291</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>51.36</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>293</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>52.02</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>295</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>297</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>52.61</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>299</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>53.23</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>301</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>53.51</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>303</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>53.47</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>305</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>307</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>309</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>52.49</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>311</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>53.19</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>313</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>53.74</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>291</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>47.69</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>293</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>295</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>47.63</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>297</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>48.26</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>299</v>
       </c>
@@ -6337,7 +6337,7 @@
         <v>48.86</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>301</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>49.34</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>303</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>49.54</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>305</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>49.53</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>307</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>50.15</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>309</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>49.18</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>311</v>
       </c>
@@ -6529,7 +6529,7 @@
         <v>49.89</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>313</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>291</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>293</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>51.74</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>295</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>51.55</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>297</v>
       </c>
@@ -6689,7 +6689,7 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>299</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>52.34</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>301</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>52.86</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>303</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>52.47</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>305</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>52.14</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>307</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>52.76</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>309</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>311</v>
       </c>
@@ -6913,7 +6913,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>313</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>52.94</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>291</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>52.69</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>293</v>
       </c>
@@ -7009,7 +7009,7 @@
         <v>53.79</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>295</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>53.02</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>297</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>53.36</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>299</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>54.18</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>301</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>54.79</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>303</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>54.42</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>305</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>54.16</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>307</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>54.83</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>309</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>53.72</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>311</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>54.29</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>313</v>
       </c>
@@ -7329,7 +7329,7 @@
         <v>54.92</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>291</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>54.54</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>293</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>55.95</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>295</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>297</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>299</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>56.58</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>301</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>57.11</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>303</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>56.68</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>305</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>56.31</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>307</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>56.97</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>309</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>55.84</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>311</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>56.61</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>313</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>57.23</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>291</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>56.38</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>293</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>57.81</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>295</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>57.07</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>297</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>56.86</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>299</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>57.24</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>301</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>57.89</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>303</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>57.48</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>305</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>56.77</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>307</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>57.38</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>309</v>
       </c>
@@ -8033,7 +8033,7 @@
         <v>56.28</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>311</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>313</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>58.28</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>291</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>56.88</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>293</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>57.79</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>295</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>57.49</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>297</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>57.88</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>299</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>58.54</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>301</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>59.18</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>303</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>58.65</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>305</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>58.25</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>307</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>59.04</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>309</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>57.92</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>311</v>
       </c>
@@ -8456,13 +8456,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B348"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B333"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>367</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>45474</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>45475</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>13185</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>45476</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>13170</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45477</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>13225</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>45478</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>13200</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45481</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>13175</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>45482</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>12888</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45483</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>12638</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>45484</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>12718</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45485</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>12729</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>45488</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>12640</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45489</v>
       </c>
@@ -8566,7 +8566,7 @@
         <v>12723</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>45490</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>12738</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45491</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>12740</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>45492</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>12725</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45495</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>12810</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>45496</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>12804</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45497</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>12757</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>45498</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>12775</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>45499</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>12965</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>45502</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>45503</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>13050</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>45504</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>13036</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>45505</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>13040</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>45506</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>13105</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>45509</v>
       </c>
@@ -8678,7 +8678,7 @@
         <v>13209</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>45510</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>13119</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>45511</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>13054</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>45512</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>12939</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>45513</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>12918</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>45516</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>12830</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>45517</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>12782</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>45518</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>12677</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>45519</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>12520</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>45520</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>12588</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>45523</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>12625</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>45524</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>12675</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>45525</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>12745</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>45526</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>12868</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>45527</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>12959</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>45530</v>
       </c>
@@ -8798,7 +8798,7 @@
         <v>13089</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>45531</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>13233</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>45532</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>13235</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>45533</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>13155</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>45534</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>13328</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>45537</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>13242</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>45538</v>
       </c>
@@ -8846,7 +8846,7 @@
         <v>13342</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45539</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>13212</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>45540</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>13131</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>45541</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>45544</v>
       </c>
@@ -8878,7 +8878,7 @@
         <v>13058</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>45545</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>13089</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>45546</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>13118</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>45547</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>13070</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>45548</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>13035</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>45552</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>12925</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>45553</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>45554</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>13358</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>45555</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>13407</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>45558</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>13640</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>45559</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>13570</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>45560</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>13759</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>45561</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>13928</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>45562</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>14004</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>45565</v>
       </c>
@@ -8990,7 +8990,7 @@
         <v>13978</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>45566</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>14106</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>45567</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>14027</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>45568</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>45569</v>
       </c>
@@ -9022,7 +9022,7 @@
         <v>14322</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>45572</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>14242</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>45573</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>14040</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>45574</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>14078</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>45575</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>14029</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>45576</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>14262</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>45579</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>14135</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>45580</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>13977</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>45581</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>45582</v>
       </c>
@@ -9094,7 +9094,7 @@
         <v>14038</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>45583</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>45586</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>14020</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>45587</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>14183</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>45588</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>14337</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>45589</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>14507</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>45590</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>14721</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>45593</v>
       </c>
@@ -9150,7 +9150,7 @@
         <v>14685</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>45594</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>14750</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>45595</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>14810</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>45596</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>14888</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>45597</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>15118</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>45600</v>
       </c>
@@ -9190,7 +9190,7 @@
         <v>15350</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>45601</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>15310</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>45602</v>
       </c>
@@ -9206,7 +9206,7 @@
         <v>15330</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>45603</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>15430</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>45604</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>15544</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>45607</v>
       </c>
@@ -9230,7 +9230,7 @@
         <v>15788</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>45608</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>15738</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>45609</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>15367</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>45610</v>
       </c>
@@ -9254,7 +9254,7 @@
         <v>15254</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>45611</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>15350</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>45614</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>15255</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>45615</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>15365</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>45616</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>45617</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>45618</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>14813</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>45621</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>14964</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>45622</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>15165</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>45624</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>15245</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>45625</v>
       </c>
@@ -9334,7 +9334,7 @@
         <v>15584</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>45628</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>15656</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>45629</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>15788</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>45630</v>
       </c>
@@ -9358,7 +9358,7 @@
         <v>15900</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>45631</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>15976</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>45632</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>45635</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>15940</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>45636</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>15760</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>45637</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>15675</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>45638</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>15602</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>45639</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>15553</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>45642</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>15589</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>45643</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>15327</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>45644</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>14919</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>45645</v>
       </c>
@@ -9446,7 +9446,7 @@
         <v>14646</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>45646</v>
       </c>
@@ -9454,7 +9454,7 @@
         <v>14684</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>45649</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>45650</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>14858</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>45660</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>14454</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>45663</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>14253</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>45664</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>14157</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>45665</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>14069</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>45666</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>13852</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>45667</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>13895</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>45670</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>45671</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>14188</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>45672</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>45673</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>13712</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>45674</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>13585</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>45677</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>13725</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>45678</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>13816</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>45679</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>13670</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>45680</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>13533</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>45681</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>13605</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>45687</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>13750</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>45688</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>13889</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>45691</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>45692</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>14008</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>45693</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>14150</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>45694</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>14265</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>45695</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>45698</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>14639</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>45699</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>14740</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>45700</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>45701</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>14802</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>45702</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>14888</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>45705</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>14850</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>45706</v>
       </c>
@@ -9710,7 +9710,7 @@
         <v>14900</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>45707</v>
       </c>
@@ -9718,7 +9718,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>45708</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>45709</v>
       </c>
@@ -9734,7 +9734,7 @@
         <v>15425</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>45712</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>45713</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>15400</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>45714</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>15320</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>45715</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>15108</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>45716</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>15162</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>45719</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>45720</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>14740</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>45721</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>14800</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>45722</v>
       </c>
@@ -9806,7 +9806,7 @@
         <v>14933</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>45723</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>15135</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>45726</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>15105</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>45727</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>14980</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>45728</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>15075</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>45729</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>15150</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>45730</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>15150</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>45733</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>15100</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>45734</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>15050</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>45735</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>15118</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>45736</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>15167</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>45737</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>14988</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>45740</v>
       </c>
@@ -9902,7 +9902,7 @@
         <v>14843</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>45741</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>14781</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>45742</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>14800</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>45756</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>14288</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>45757</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>14387</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>45758</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>45761</v>
       </c>
@@ -9950,7 +9950,7 @@
         <v>14260</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>45762</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>14177</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>45763</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>45764</v>
       </c>
@@ -9974,7 +9974,7 @@
         <v>14225</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="5">
         <v>45768</v>
       </c>
@@ -9982,7 +9982,7 @@
         <v>14001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>45769</v>
       </c>
@@ -9990,7 +9990,7 @@
         <v>14401</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="5">
         <v>45770</v>
       </c>
@@ -9998,7 +9998,7 @@
         <v>14501</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>45771</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>14488</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>45772</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>14470</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>45775</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>14006</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
         <v>45776</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>45777</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>45779</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>13891</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>45782</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>45783</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>13316</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>45784</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>13130</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>45785</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>45786</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>13150</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>45791</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>13422</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>45792</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>13373</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="5">
         <v>45793</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>13211</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>45796</v>
       </c>
@@ -10118,7 +10118,7 @@
         <v>13256</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>45797</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>45798</v>
       </c>
@@ -10134,7 +10134,7 @@
         <v>13400</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>45799</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>45800</v>
       </c>
@@ -10150,7 +10150,7 @@
         <v>13361</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>45803</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>13125</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>45804</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>13180</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>45805</v>
       </c>
@@ -10174,7 +10174,7 @@
         <v>13315</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>45810</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>13331</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>45811</v>
       </c>
@@ -10190,7 +10190,7 @@
         <v>13386</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>45812</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>13385</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>45813</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>13343</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>45818</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>13328</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>45819</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>13145</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>45820</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>13225</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
         <v>45821</v>
       </c>
@@ -10238,7 +10238,7 @@
         <v>13360</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>45824</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>45825</v>
       </c>
@@ -10254,7 +10254,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>45826</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>13615</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
         <v>45827</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>13677</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>45828</v>
       </c>
@@ -10278,7 +10278,7 @@
         <v>13655</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
         <v>45831</v>
       </c>
@@ -10286,7 +10286,7 @@
         <v>13730</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>45832</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>13415</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
         <v>45833</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>45834</v>
       </c>
@@ -10310,7 +10310,7 @@
         <v>13550</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
         <v>45838</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>13550</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>45839</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>13575</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
         <v>45840</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>45841</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
         <v>45842</v>
       </c>
@@ -10350,7 +10350,7 @@
         <v>13850</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>45845</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="5">
         <v>45846</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>13975</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>45847</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="5">
         <v>45848</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
         <v>45849</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>14200</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>45852</v>
       </c>
@@ -10398,7 +10398,7 @@
         <v>14245</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>45853</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
         <v>45854</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>14350</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
         <v>45855</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>14360</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>45856</v>
       </c>
@@ -10430,7 +10430,7 @@
         <v>14555</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
         <v>45859</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>14576</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
         <v>45860</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>14550</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
         <v>45861</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>14666</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
         <v>45862</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
         <v>45863</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>45866</v>
       </c>
@@ -10478,7 +10478,7 @@
         <v>14494</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="5">
         <v>45867</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>14575</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>45868</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="5">
         <v>45869</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>14635</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>45870</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="5">
         <v>45873</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>45874</v>
       </c>
@@ -10526,7 +10526,7 @@
         <v>14689</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="5">
         <v>45875</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>45876</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>14530</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="5">
         <v>45877</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>14605</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
         <v>45880</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="5">
         <v>45881</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>14825</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="5">
         <v>45882</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
         <v>45883</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>14707</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="5">
         <v>45884</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>14705</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>45888</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="5">
         <v>45889</v>
       </c>
@@ -10606,7 +10606,7 @@
         <v>14642</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
         <v>45890</v>
       </c>
@@ -10614,7 +10614,7 @@
         <v>14580</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="5">
         <v>45891</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
         <v>45894</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>14699</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="5">
         <v>45895</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>14570</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
         <v>45896</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="5">
         <v>45897</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>14550</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
         <v>45898</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="5">
         <v>45901</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
         <v>45902</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="5">
         <v>45903</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="5">
         <v>45904</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>14665</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
         <v>45908</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>14601</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
         <v>45909</v>
       </c>
@@ -10710,7 +10710,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="5">
         <v>45910</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="5">
         <v>45911</v>
       </c>
@@ -10726,7 +10726,7 @@
         <v>14540</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
         <v>45912</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
         <v>45915</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>14528</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
         <v>45916</v>
       </c>
@@ -10750,7 +10750,7 @@
         <v>14590</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="5">
         <v>45917</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>14710</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="5">
         <v>45918</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>14623</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="5">
         <v>45919</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>14661</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="5">
         <v>45922</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="5">
         <v>45923</v>
       </c>
@@ -10790,7 +10790,7 @@
         <v>14475</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="5">
         <v>45924</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>14498</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="5">
         <v>45925</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="5">
         <v>45926</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>14678</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="5">
         <v>45929</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="5">
         <v>45930</v>
       </c>
@@ -10830,7 +10830,7 @@
         <v>14545</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="5">
         <v>45931</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>14575</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
         <v>45932</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>14750</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="5">
         <v>45933</v>
       </c>
@@ -10854,7 +10854,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="5">
         <v>45936</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="5">
         <v>45937</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>14751</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="5">
         <v>45938</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>14901</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="5">
         <v>45939</v>
       </c>
@@ -10886,7 +10886,7 @@
         <v>14999</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="5">
         <v>45940</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>14942</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="5">
         <v>45943</v>
       </c>
@@ -10902,7 +10902,7 @@
         <v>14545</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="5">
         <v>45944</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>14603</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="5">
         <v>45945</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="5">
         <v>45946</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="5">
         <v>45947</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="5">
         <v>45950</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>14611</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="5">
         <v>45951</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>14711</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="5">
         <v>45952</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>14556</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="5">
         <v>45953</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>15526</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="5">
         <v>45954</v>
       </c>
@@ -10974,276 +10974,156 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="5">
         <v>45957</v>
       </c>
       <c r="B315">
-        <v>15530</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14475</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="5">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B316">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14188</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="5">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B317">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14123</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="5">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B318">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13900</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="5">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="B319">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13833</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="5">
-        <v>45962</v>
+        <v>45967</v>
       </c>
       <c r="B320">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13828</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="5">
-        <v>45963</v>
+        <v>45971</v>
       </c>
       <c r="B321">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13700</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="5">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="B322">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="5">
-        <v>45965</v>
+        <v>45974</v>
       </c>
       <c r="B323">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="5">
-        <v>45966</v>
+        <v>45975</v>
       </c>
       <c r="B324">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13775</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="5">
-        <v>45967</v>
+        <v>45978</v>
       </c>
       <c r="B325">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13870</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="5">
-        <v>45968</v>
+        <v>45979</v>
       </c>
       <c r="B326">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14007</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="5">
-        <v>45969</v>
+        <v>45980</v>
       </c>
       <c r="B327">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14135</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="5">
-        <v>45970</v>
+        <v>45981</v>
       </c>
       <c r="B328">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14066</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="5">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="B329">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14025</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="5">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="B330">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14025</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="5">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="B331">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13990</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="5">
-        <v>45974</v>
+        <v>45987</v>
       </c>
       <c r="B332">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+        <v>14030</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="5">
-        <v>45975</v>
+        <v>45988</v>
       </c>
       <c r="B333">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A334" s="5">
-        <v>45976</v>
-      </c>
-      <c r="B334">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A335" s="5">
-        <v>45977</v>
-      </c>
-      <c r="B335">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A336" s="5">
-        <v>45978</v>
-      </c>
-      <c r="B336">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A337" s="5">
-        <v>45979</v>
-      </c>
-      <c r="B337">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A338" s="5">
-        <v>45980</v>
-      </c>
-      <c r="B338">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A339" s="5">
-        <v>45981</v>
-      </c>
-      <c r="B339">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A340" s="5">
-        <v>45982</v>
-      </c>
-      <c r="B340">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A341" s="5">
-        <v>45983</v>
-      </c>
-      <c r="B341">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A342" s="5">
-        <v>45984</v>
-      </c>
-      <c r="B342">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A343" s="5">
-        <v>45985</v>
-      </c>
-      <c r="B343">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A344" s="5">
-        <v>45986</v>
-      </c>
-      <c r="B344">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A345" s="5">
-        <v>45987</v>
-      </c>
-      <c r="B345">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A346" s="5">
-        <v>45988</v>
-      </c>
-      <c r="B346">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A347" s="5">
-        <v>45989</v>
-      </c>
-      <c r="B347">
-        <v>14505</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A348" s="5">
-        <v>45990</v>
-      </c>
-      <c r="B348">
-        <v>14505</v>
+        <v>14200</v>
       </c>
     </row>
   </sheetData>
